--- a/data/export/2026-10-26-浦东35路.xlsx
+++ b/data/export/2026-10-26-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1381,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1492,1339 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-26-浦东35路.xlsx
+++ b/data/export/2026-10-26-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC21"/>
+  <dimension ref="A1:AC30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,33 +693,37 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -743,32 +751,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -776,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,33 +812,37 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -887,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -937,7 +953,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -965,32 +981,36 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>160分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -998,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1022,17 +1042,17 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1042,13 +1062,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1159,7 +1183,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1244,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1294,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1355,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1405,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1466,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1516,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1577,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1627,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1688,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1714,7 +1738,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1799,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1825,7 +1849,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1910,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1936,7 +1960,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1997,7 +2021,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2047,7 +2071,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2132,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2158,7 +2182,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2243,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2269,7 +2293,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2354,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2380,7 +2404,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2465,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2491,7 +2515,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2576,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2602,7 +2626,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2687,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2713,7 +2737,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2798,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2824,7 +2848,1014 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>2/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>1/27</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-26-浦东35路.xlsx
+++ b/data/export/2026-10-26-浦东35路.xlsx
@@ -642,12 +642,12 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -870,32 +870,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -903,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -927,17 +931,17 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -947,13 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -991,12 +999,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>160分钟</t>
+          <t>159分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
@@ -1018,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1067,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>159.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1355,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1466,7 +1474,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1577,7 +1585,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1688,7 +1696,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1799,7 +1807,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1910,7 +1918,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2021,7 +2029,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2132,7 +2140,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2354,7 +2362,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2465,7 +2473,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2576,7 +2584,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2687,7 +2695,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2798,7 +2806,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2909,7 +2917,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3020,7 +3028,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3131,7 +3139,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3242,7 +3250,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3353,7 +3361,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3464,7 +3472,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3575,7 +3583,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3686,7 +3694,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3740,7 +3748,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -3801,7 +3809,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3850,7 +3858,7 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">

--- a/data/export/2026-10-26-浦东35路.xlsx
+++ b/data/export/2026-10-26-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC30"/>
+  <dimension ref="A1:AC39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,7 +436,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
@@ -446,10 +446,10 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -761,24 +761,24 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>155分钟</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,17 +946,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,14 +1065,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
           <t>159.0</t>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1219,32 +1219,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1252,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1276,33 +1280,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -1330,32 +1338,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>160分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1363,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1387,33 +1399,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -1441,32 +1457,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>159分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1474,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1498,33 +1518,37 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -1552,32 +1576,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -1585,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1609,33 +1637,37 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1735,7 +1767,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1807,7 +1839,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1846,7 +1878,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1885,12 +1917,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程33%处后消失；随后反向物理轨迹由seq38推进至seq49，推进11站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1918,7 +1950,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1926,10 +1958,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr"/>
-      <c r="R13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>物理seq22（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
       <c r="S13" s="2" t="inlineStr"/>
-      <c r="T13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq22映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
           <t>07:12</t>
@@ -2029,7 +2073,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2140,7 +2184,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2218,12 +2262,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq39推进至seq49，推进10站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2251,7 +2295,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2259,10 +2303,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q16" s="2" t="inlineStr"/>
-      <c r="R16" s="2" t="inlineStr"/>
-      <c r="S16" s="2" t="inlineStr"/>
-      <c r="T16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq39（站名待映射） ETA 3分钟参与校验</t>
+        </is>
+      </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
           <t>07:24</t>
@@ -2362,7 +2422,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2473,7 +2533,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2584,7 +2644,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2695,7 +2755,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2806,7 +2866,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2917,7 +2977,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3028,7 +3088,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3139,7 +3199,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3250,7 +3310,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3361,7 +3421,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3472,7 +3532,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3583,7 +3643,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3694,7 +3754,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3743,7 +3803,7 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3809,7 +3869,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3867,6 +3927,1029 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>2/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>6/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A72305D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>08:41</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>4/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>8/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>6/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>4/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-26-浦东35路.xlsx
+++ b/data/export/2026-10-26-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC39"/>
+  <dimension ref="A1:AC47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -1695,32 +1695,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1728,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1752,17 +1756,17 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
@@ -1772,13 +1776,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -1806,32 +1814,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>169分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1839,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1863,17 +1875,17 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
@@ -1883,13 +1895,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>169.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>14/27</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1938,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程33%处后消失；随后反向物理轨迹由seq38推进至seq49，推进11站，达到≥2站确认条件</t>
+          <t>原方向在全程33%处后消失；随后反向物理轨迹由seq38推进至seq59，推进21站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1950,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2040,32 +2056,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>160分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -2073,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2097,33 +2117,37 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2223,7 +2247,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2267,7 +2291,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq39推进至seq49，推进10站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq39推进至seq62，推进23站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2295,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2422,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2461,7 +2485,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2500,32 +2524,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2533,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2557,33 +2585,37 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2683,7 +2715,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2722,32 +2754,36 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>164分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2755,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2779,33 +2815,37 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>164.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -2833,32 +2873,36 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2866,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2890,33 +2934,37 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -2977,7 +3025,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3016,7 +3064,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3088,7 +3136,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3199,7 +3247,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3310,7 +3358,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3421,7 +3469,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3532,7 +3580,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3643,7 +3691,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3754,7 +3802,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3808,7 +3856,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -3869,7 +3917,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3984,7 +4032,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4099,7 +4147,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4153,7 +4201,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4373,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4379,7 +4427,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4488,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4494,7 +4542,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -4555,7 +4603,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4609,7 +4657,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4718,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4724,7 +4772,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -4785,7 +4833,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4829,13 +4877,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB38" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -4896,7 +4948,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4940,11 +4992,919 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>169.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>14/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB39" s="2" t="inlineStr"/>
-      <c r="AC39" s="2" t="inlineStr">
+      <c r="AB40" s="2" t="inlineStr"/>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>11/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr"/>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>6/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr"/>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>4/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>164.0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>13/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr"/>
+      <c r="AC47" s="2" t="inlineStr">
         <is>
           <t>—/27</t>
         </is>

--- a/data/export/2026-10-26-浦东35路.xlsx
+++ b/data/export/2026-10-26-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC47"/>
+  <dimension ref="A1:AC53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1300,17 +1300,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>16/27</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>15/27</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>14/27</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>14/27</t>
+          <t>19/27</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>16/27</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>12/27</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>18/27</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3103,32 +3103,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -3136,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3160,33 +3164,37 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -3214,32 +3222,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3247,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3271,17 +3283,17 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -3291,13 +3303,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>12/27</t>
         </is>
       </c>
     </row>
@@ -3325,32 +3341,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3358,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3382,17 +3402,17 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
@@ -3402,13 +3422,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3508,7 +3532,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3547,32 +3571,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3580,7 +3608,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3604,33 +3632,37 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -3658,32 +3690,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3691,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3715,17 +3751,17 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
@@ -3735,13 +3771,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB28" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -3769,32 +3809,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3802,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3826,17 +3870,17 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
@@ -3846,17 +3890,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -3884,32 +3928,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3917,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3941,17 +3989,17 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -3961,17 +4009,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -3999,32 +4047,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4032,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4056,37 +4108,37 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -4114,32 +4166,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4147,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4171,37 +4227,37 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -4340,32 +4396,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -4373,7 +4433,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4397,17 +4457,17 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4417,17 +4477,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -4488,7 +4548,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4542,7 +4602,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>16/27</t>
         </is>
       </c>
     </row>
@@ -4603,7 +4663,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4642,7 +4702,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4657,7 +4717,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>15/27</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4778,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4772,7 +4832,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>14/27</t>
         </is>
       </c>
     </row>
@@ -4833,7 +4893,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4887,7 +4947,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -4948,7 +5008,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5002,7 +5062,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>14/27</t>
+          <t>19/27</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5123,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5174,7 +5234,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5228,7 +5288,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>16/27</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5349,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5400,7 +5460,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5454,7 +5514,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>12/27</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5575,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5626,7 +5686,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5680,7 +5740,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -5741,7 +5801,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5795,7 +5855,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>18/27</t>
         </is>
       </c>
     </row>
@@ -5803,22 +5863,22 @@
       <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -5851,12 +5911,12 @@
       <c r="M47" s="2" t="inlineStr"/>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5870,43 +5930,729 @@
       <c r="T47" s="2" t="inlineStr"/>
       <c r="U47" s="2" t="inlineStr">
         <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>6/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
           <t>11:20</t>
         </is>
       </c>
-      <c r="V47" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W47" s="2" t="inlineStr">
+      <c r="W48" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X47" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y47" s="2" t="inlineStr">
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z47" s="2" t="inlineStr">
+      <c r="Z48" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
+      <c r="AA48" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB47" s="2" t="inlineStr"/>
-      <c r="AC47" s="2" t="inlineStr">
+      <c r="AB48" s="2" t="inlineStr"/>
+      <c r="AC48" s="2" t="inlineStr">
         <is>
           <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>4/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr"/>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>11/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>1/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>15/27</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-26-浦东35路.xlsx
+++ b/data/export/2026-10-26-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC53"/>
+  <dimension ref="A1:AC59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,14 +708,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>135.0</t>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1538,17 +1538,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>15/27</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1657,17 +1657,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>14/27</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1776,17 +1776,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1895,17 +1895,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>169.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>19/27</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2137,17 +2137,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2385,7 +2385,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2496,7 +2496,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>18/27</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       <c r="AB22" s="2" t="inlineStr"/>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/27</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3543,7 +3543,7 @@
       <c r="AB26" s="2" t="inlineStr"/>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4004,14 +4004,14 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
           <t>135.0</t>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -4176,12 +4176,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -4368,7 +4368,7 @@
       <c r="AB33" s="2" t="inlineStr"/>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4406,12 +4406,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -4515,32 +4515,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4548,7 +4552,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4572,17 +4576,17 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -4592,17 +4596,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -4630,32 +4634,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -4663,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4687,17 +4695,17 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4707,17 +4715,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>15/27</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -4745,32 +4753,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -4778,7 +4790,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4802,17 +4814,17 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -4822,17 +4834,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>14/27</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -4860,32 +4872,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -4893,7 +4909,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4917,17 +4933,17 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -4937,17 +4953,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -4975,32 +4991,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -5008,7 +5028,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5032,17 +5052,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5052,17 +5072,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>169.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>19/27</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -5123,7 +5143,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5162,7 +5182,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5173,7 +5193,7 @@
       <c r="AB40" s="2" t="inlineStr"/>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -5201,32 +5221,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5234,7 +5258,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5258,17 +5282,17 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5278,17 +5302,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -5349,7 +5373,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5399,7 +5423,7 @@
       <c r="AB42" s="2" t="inlineStr"/>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -5460,7 +5484,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5514,7 +5538,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -5575,7 +5599,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5614,7 +5638,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5625,7 +5649,7 @@
       <c r="AB44" s="2" t="inlineStr"/>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -5686,7 +5710,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5740,7 +5764,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5825,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5855,7 +5879,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>18/27</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -5916,7 +5940,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5970,7 +5994,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -6031,7 +6055,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6081,7 +6105,7 @@
       <c r="AB48" s="2" t="inlineStr"/>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6142,7 +6166,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6196,7 +6220,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -6257,7 +6281,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6307,7 +6331,7 @@
       <c r="AB50" s="2" t="inlineStr"/>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6392,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6417,12 +6441,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -6483,7 +6507,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6537,7 +6561,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -6598,7 +6622,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6642,17 +6666,687 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>5/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB53" s="2" t="inlineStr">
-        <is>
-          <t>159.0</t>
-        </is>
-      </c>
-      <c r="AC53" s="2" t="inlineStr">
-        <is>
-          <t>15/27</t>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr"/>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr"/>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr"/>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr"/>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr"/>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-26-浦东35路.xlsx
+++ b/data/export/2026-10-26-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC59"/>
+  <dimension ref="A1:AC64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,14 +827,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>146.0</t>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2490,13 +2490,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2600,22 +2604,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2720,13 +2724,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2835,12 +2843,12 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2910,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2954,17 +2962,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -3025,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3064,18 +3072,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3179,17 +3191,17 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3313,7 +3325,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3444,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3537,13 +3549,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3647,17 +3663,17 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3781,7 +3797,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3885,14 +3901,14 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
           <t>146.0</t>
@@ -3900,7 +3916,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -3965,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4019,7 +4035,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4138,7 +4154,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4257,7 +4273,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -4487,7 +4503,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4622,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4725,7 +4741,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4860,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -4963,7 +4979,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -5082,7 +5098,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -5143,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5312,7 +5328,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -5340,32 +5356,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5373,7 +5393,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5397,17 +5417,17 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
@@ -5417,13 +5437,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB42" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -5451,32 +5475,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5484,7 +5512,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5508,37 +5536,37 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -5566,32 +5594,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -5599,7 +5631,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5623,17 +5655,17 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5643,13 +5675,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB44" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -5677,32 +5713,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5710,7 +5750,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5734,17 +5774,17 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5754,17 +5794,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -5792,32 +5832,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5825,7 +5869,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5849,17 +5893,17 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -5869,12 +5913,12 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -5907,32 +5951,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -5940,7 +5988,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5964,32 +6012,32 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6022,32 +6070,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -6055,7 +6107,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6079,33 +6131,37 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB48" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -6133,32 +6189,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6166,7 +6226,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6190,32 +6250,32 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6248,32 +6308,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -6281,7 +6345,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6305,17 +6369,17 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -6325,13 +6389,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB50" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -6392,7 +6460,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6446,7 +6514,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -6507,7 +6575,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6561,7 +6629,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -6622,7 +6690,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6676,7 +6744,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -6737,7 +6805,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6791,7 +6859,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -6852,7 +6920,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6963,7 +7031,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7074,7 +7142,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7185,7 +7253,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7296,7 +7364,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7340,13 +7408,592 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB59" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>140.5</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>12/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>10/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>5/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>17/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-26-浦东35路.xlsx
+++ b/data/export/2026-10-26-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC64"/>
+  <dimension ref="A1:AC68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,14 +1414,14 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
           <t>147.5</t>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,22 +1533,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1890,14 +1890,14 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
           <t>150.5</t>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4144,17 +4144,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4258,22 +4258,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4607,14 +4607,14 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
           <t>147.5</t>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4726,22 +4726,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5083,14 +5083,14 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
           <t>150.5</t>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -5512,7 +5512,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -5631,7 +5631,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6107,7 +6107,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6427,32 +6427,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6460,7 +6464,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6484,37 +6488,37 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -6542,32 +6546,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>120分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6575,7 +6583,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6599,17 +6607,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6619,17 +6627,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -6657,32 +6665,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -6690,7 +6702,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6714,37 +6726,37 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -6805,7 +6817,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6887,12 +6899,12 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq46，推进8站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -6920,7 +6932,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6928,10 +6940,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q55" s="2" t="inlineStr"/>
-      <c r="R55" s="2" t="inlineStr"/>
-      <c r="S55" s="2" t="inlineStr"/>
-      <c r="T55" s="2" t="inlineStr"/>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="S55" s="2" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="T55" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq38（站名待映射） ETA 8分钟参与校验</t>
+        </is>
+      </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
@@ -7031,7 +7059,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7142,7 +7170,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7253,7 +7281,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7364,7 +7392,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7479,7 +7507,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7533,7 +7561,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7622,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7709,7 +7737,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7824,7 +7852,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7939,7 +7967,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -7993,7 +8021,467 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
+          <t>18/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
           <t>17/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>147.5</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>19/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>137.7</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>11/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>150.5</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>22/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-26-浦东35路.xlsx
+++ b/data/export/2026-10-26-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC68"/>
+  <dimension ref="A1:AC70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,18 +2017,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2132,14 +2136,14 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
           <t>143.5</t>
@@ -2147,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2319,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2565,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2619,7 +2623,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2853,7 +2857,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -2972,7 +2976,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3087,7 +3091,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3206,7 +3210,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -3325,7 +3329,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -3444,7 +3448,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3628,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3678,7 +3682,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -3797,7 +3801,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3916,7 +3920,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -3981,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4025,17 +4029,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4273,7 +4277,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4507,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4622,7 +4626,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4741,7 +4745,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4864,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -4979,7 +4983,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5098,7 +5102,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5163,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5274,7 +5278,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5313,14 +5317,14 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
           <t>143.5</t>
@@ -5328,7 +5332,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -5512,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5566,7 +5570,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -5631,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5804,7 +5808,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -5923,7 +5927,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -5988,7 +5992,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6042,7 +6046,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -6107,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6161,7 +6165,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -6226,7 +6230,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6280,7 +6284,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -6464,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6518,7 +6522,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6691,12 @@
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6702,7 +6706,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6756,7 +6760,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -6784,32 +6788,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6817,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6841,17 +6849,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6861,17 +6869,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -6904,7 +6912,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq46，推进8站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq53，推进15站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -6932,7 +6940,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7026,32 +7034,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7059,7 +7071,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7083,33 +7095,37 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB56" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7186,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7281,7 +7297,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7392,7 +7408,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7507,7 +7523,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7561,7 +7577,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -7622,7 +7638,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7676,7 +7692,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -7737,7 +7753,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7791,7 +7807,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -7852,7 +7868,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7906,7 +7922,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -7967,7 +7983,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8021,7 +8037,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -8082,7 +8098,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8136,7 +8152,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -8197,7 +8213,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8251,7 +8267,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -8312,7 +8328,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8366,7 +8382,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -8427,7 +8443,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8481,7 +8497,237 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>5/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>143.5</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>15/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-26-浦东35路.xlsx
+++ b/data/export/2026-10-26-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC70"/>
+  <dimension ref="A1:AC74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2256,13 +2256,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2383,13 +2387,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -2504,7 +2512,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2577,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2613,17 +2621,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2728,17 +2736,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2842,14 +2850,14 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
           <t>148.0</t>
@@ -2857,7 +2865,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -2976,7 +2984,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3081,17 +3089,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3164,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3200,17 +3208,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3314,14 +3322,14 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
           <t>153.0</t>
@@ -3329,7 +3337,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3456,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -3563,7 +3571,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3682,7 +3690,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -3801,7 +3809,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3920,7 +3928,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4034,12 +4042,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4166,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4277,7 +4285,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -4388,7 +4396,7 @@
       <c r="AB33" s="2" t="inlineStr"/>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -4507,7 +4515,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -4572,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4626,7 +4634,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4745,7 +4753,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4872,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -4983,7 +4991,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5102,7 +5110,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -5163,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5207,13 +5215,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB40" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5332,7 +5344,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -5451,7 +5463,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5560,17 +5572,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -5635,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5679,17 +5691,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5820,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5912,14 +5924,14 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
           <t>148.0</t>
@@ -5927,7 +5939,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -5992,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6036,17 +6048,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6155,17 +6167,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6284,7 +6296,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -6403,7 +6415,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6522,7 +6534,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -6641,7 +6653,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -6706,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6760,7 +6772,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -6798,12 +6810,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
@@ -6825,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6874,12 +6886,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -6912,7 +6924,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq53，推进15站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq58，推进20站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -6940,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7006,7 +7018,7 @@
       <c r="AB55" s="2" t="inlineStr"/>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -7044,12 +7056,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
@@ -7071,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7120,12 +7132,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7153,32 +7165,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7186,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7210,17 +7226,17 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7230,13 +7246,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB57" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -7264,32 +7284,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -7297,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7321,17 +7345,17 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7341,13 +7365,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB58" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -7375,32 +7403,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7408,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7432,17 +7464,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7452,17 +7484,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -7490,32 +7522,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -7523,7 +7559,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7547,17 +7583,17 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
@@ -7567,17 +7603,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -7605,32 +7641,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7638,7 +7678,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7662,17 +7702,17 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
@@ -7682,17 +7722,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -7720,32 +7760,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -7753,7 +7797,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7777,17 +7821,17 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
@@ -7797,17 +7841,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -7868,7 +7912,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7922,7 +7966,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -7983,7 +8027,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8037,7 +8081,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8142,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8152,7 +8196,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -8213,7 +8257,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8267,7 +8311,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -8328,7 +8372,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8382,7 +8426,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8487,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8497,7 +8541,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -8558,7 +8602,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8607,12 +8651,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -8620,22 +8664,22 @@
       <c r="A70" s="2" t="inlineStr"/>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -8668,12 +8712,12 @@
       <c r="M70" s="2" t="inlineStr"/>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8712,22 +8756,474 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr"/>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA70" s="2" t="inlineStr">
+      <c r="AA71" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB70" s="2" t="inlineStr">
+      <c r="AB71" s="2" t="inlineStr">
         <is>
           <t>143.5</t>
         </is>
       </c>
-      <c r="AC70" s="2" t="inlineStr">
-        <is>
-          <t>15/28</t>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>17/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr"/>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>26/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>23/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-26-浦东35路.xlsx
+++ b/data/export/2026-10-26-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC74"/>
+  <dimension ref="A1:AC83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,14 +1295,14 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
           <t>144.5</t>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1652,14 +1652,14 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
           <t>144.0</t>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>137.3</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3680,17 +3680,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4032,7 +4032,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4275,17 +4275,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4500,14 +4500,14 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
           <t>144.5</t>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4624,17 +4624,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4857,14 +4857,14 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
           <t>144.0</t>
@@ -4872,7 +4872,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>137.3</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6172,12 +6172,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6286,17 +6286,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -6361,7 +6361,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6480,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6524,17 +6524,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -6599,7 +6599,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -6837,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6876,7 +6876,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7360,7 +7360,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7532,24 +7532,24 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7608,7 +7608,7 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>137.3</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7663,12 +7663,12 @@
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7678,7 +7678,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7770,24 +7770,24 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -7879,32 +7879,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7912,7 +7916,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7936,17 +7940,17 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
@@ -7956,17 +7960,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -7994,32 +7998,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8027,7 +8035,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8051,17 +8059,17 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -8071,17 +8079,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -8109,32 +8117,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8142,7 +8154,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8166,17 +8178,17 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
@@ -8186,17 +8198,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -8224,32 +8236,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8257,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8281,17 +8297,17 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
@@ -8301,17 +8317,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -8372,7 +8388,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8426,7 +8442,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -8487,7 +8503,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8602,7 +8618,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8717,7 +8733,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8828,7 +8844,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8882,7 +8898,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -8943,7 +8959,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9054,7 +9070,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9169,7 +9185,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9227,6 +9243,1041 @@
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>16/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>3/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>1/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>21/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>128.7</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>5/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>144.5</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>22/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>134.5</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>10/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>132.7</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>8/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>4/30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-26-浦东35路.xlsx
+++ b/data/export/2026-10-26-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC83"/>
+  <dimension ref="A1:AC88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1538,17 +1538,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>134.8</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>148.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3327,17 +3327,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4743,17 +4743,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>134.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5334,17 +5334,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>148.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -5885,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -6361,7 +6361,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6480,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6529,7 +6529,7 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6762,17 +6762,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>134.8</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -6837,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7127,12 +7127,12 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7479,7 +7479,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7613,7 +7613,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -7678,7 +7678,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -8020,12 +8020,12 @@
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -8035,7 +8035,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
@@ -8127,24 +8127,24 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>123分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8312,7 +8312,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8355,32 +8355,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -8388,7 +8392,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8412,17 +8416,17 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
@@ -8432,17 +8436,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>134.8</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -8503,7 +8507,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8557,7 +8561,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -8585,32 +8589,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -8618,7 +8626,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8642,17 +8650,17 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
@@ -8662,12 +8670,12 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8700,12 +8708,12 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq28推进至seq44，推进16站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -8733,7 +8741,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8741,10 +8749,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q70" s="2" t="inlineStr"/>
-      <c r="R70" s="2" t="inlineStr"/>
-      <c r="S70" s="2" t="inlineStr"/>
-      <c r="T70" s="2" t="inlineStr"/>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>物理seq30（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="S70" s="2" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="T70" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq30映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq28（站名待映射） ETA 1分钟参与校验</t>
+        </is>
+      </c>
       <c r="U70" s="2" t="inlineStr">
         <is>
           <t>15:35</t>
@@ -8811,32 +8835,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -8844,7 +8872,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8868,17 +8896,17 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
@@ -8888,17 +8916,17 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>148.3</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -9037,32 +9065,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9070,7 +9102,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9094,17 +9126,17 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
@@ -9114,17 +9146,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -9185,7 +9217,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9300,7 +9332,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9415,7 +9447,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9530,7 +9562,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9645,7 +9677,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9699,7 +9731,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -9760,7 +9792,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9875,7 +9907,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9929,7 +9961,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -9990,7 +10022,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10105,7 +10137,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10167,22 +10199,22 @@
       <c r="A83" s="2" t="inlineStr"/>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>17:20</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -10215,12 +10247,12 @@
       <c r="M83" s="2" t="inlineStr"/>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10259,22 +10291,597 @@
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>6/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA83" s="2" t="inlineStr">
+      <c r="AA84" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB83" s="2" t="inlineStr">
+      <c r="AB84" s="2" t="inlineStr">
         <is>
           <t>128.0</t>
         </is>
       </c>
-      <c r="AC83" s="2" t="inlineStr">
+      <c r="AC84" s="2" t="inlineStr">
         <is>
           <t>4/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>126.5</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>2/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>19/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>133.7</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>9/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>141.7</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>18/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-26-浦东35路.xlsx
+++ b/data/export/2026-10-26-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC88"/>
+  <dimension ref="A1:AC94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1890,22 +1890,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>148.3</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2387,17 +2387,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -2458,7 +2458,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2855,17 +2855,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>159.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3322,17 +3322,17 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3794,17 +3794,17 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5095,22 +5095,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5334,17 +5334,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>148.3</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5805,7 +5805,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5929,17 +5929,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>159.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -6177,7 +6177,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -6361,7 +6361,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -6772,7 +6772,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -6837,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7132,12 +7132,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -7321,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7365,17 +7365,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -7440,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7598,7 +7598,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7678,7 +7678,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7732,7 +7732,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -8035,7 +8035,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8446,7 +8446,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -8474,32 +8474,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -8507,7 +8511,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8531,37 +8535,37 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA68" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -8599,12 +8603,12 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
@@ -8626,7 +8630,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8665,7 +8669,7 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
@@ -8675,12 +8679,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -8713,7 +8717,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq28推进至seq44，推进16站，达到≥2站确认条件</t>
+          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq28推进至seq62，推进34站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -8741,7 +8745,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8835,36 +8839,32 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>158分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -8872,7 +8872,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8896,17 +8896,17 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
@@ -8916,17 +8916,17 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>148.3</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -9075,24 +9075,24 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9141,17 +9141,17 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA73" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9184,32 +9184,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>181分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -9217,7 +9221,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9241,17 +9245,17 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
@@ -9261,17 +9265,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>159.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -9299,32 +9303,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9332,7 +9340,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9356,32 +9364,32 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA75" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9414,32 +9422,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:39</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -9447,7 +9459,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9471,17 +9483,17 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
@@ -9491,17 +9503,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -9562,7 +9574,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9677,7 +9689,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9731,7 +9743,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -9792,7 +9804,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9846,7 +9858,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -9907,7 +9919,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9961,7 +9973,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -10022,7 +10034,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10076,7 +10088,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -10137,7 +10149,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10191,7 +10203,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -10252,7 +10264,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10306,7 +10318,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -10367,7 +10379,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10421,7 +10433,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -10482,7 +10494,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10597,7 +10609,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10712,7 +10724,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10766,7 +10778,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -10827,7 +10839,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10885,6 +10897,696 @@
         </is>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>132.5</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>6/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>14/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>144.5</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>22/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>137.7</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>15/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>140.5</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>16/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>24/30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-26-浦东35路.xlsx
+++ b/data/export/2026-10-26-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC94"/>
+  <dimension ref="A1:AC100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>132.2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,22 +1295,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1652,22 +1652,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1776,17 +1776,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -2458,7 +2458,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2850,17 +2850,17 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>158.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3556,22 +3556,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4156,12 +4156,12 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>132.2</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4500,22 +4500,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4857,22 +4857,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4981,17 +4981,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -5885,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5924,17 +5924,17 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>158.3</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -6177,7 +6177,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -6361,7 +6361,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6400,22 +6400,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -6534,7 +6534,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -6599,7 +6599,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6643,12 +6643,12 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>132.2</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -6837,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -7321,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7360,7 +7360,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7375,7 +7375,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -7440,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7494,7 +7494,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7613,7 +7613,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -7678,7 +7678,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7732,7 +7732,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -8035,7 +8035,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -8273,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -8511,7 +8511,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8630,7 +8630,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8684,7 +8684,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -8872,7 +8872,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8911,7 +8911,7 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -9102,7 +9102,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9194,24 +9194,24 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>181分钟</t>
+          <t>179分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9260,17 +9260,17 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA74" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>158.3</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9340,7 +9340,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -9459,7 +9459,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -9541,32 +9541,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>166分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -9574,7 +9578,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9598,37 +9602,37 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -9656,32 +9660,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -9689,7 +9697,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9713,37 +9721,37 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA78" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -9771,32 +9779,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9804,7 +9816,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9828,17 +9840,17 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
@@ -9848,12 +9860,12 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>132.2</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
@@ -9886,32 +9898,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -9919,7 +9935,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9943,37 +9959,37 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA80" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -10001,32 +10017,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -10034,7 +10054,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10058,17 +10078,17 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
@@ -10078,17 +10098,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -10149,7 +10169,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10203,7 +10223,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -10264,7 +10284,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10318,7 +10338,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10399,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10433,7 +10453,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -10494,7 +10514,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10548,7 +10568,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -10609,7 +10629,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10663,7 +10683,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -10724,7 +10744,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10778,7 +10798,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -10839,7 +10859,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10893,7 +10913,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10974,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11008,7 +11028,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -11069,7 +11089,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11123,7 +11143,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -11184,7 +11204,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11299,7 +11319,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11353,7 +11373,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -11414,7 +11434,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11468,7 +11488,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -11529,7 +11549,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11587,6 +11607,696 @@
         </is>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>23/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>143.7</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>20/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>143.5</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>19/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>135.5</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>10/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>158.3</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>26/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>143.7</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>20/30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-26-浦东35路.xlsx
+++ b/data/export/2026-10-26-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC100"/>
+  <dimension ref="A1:AC104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>141.7</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,17 +1771,17 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2256,17 +2256,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -2458,7 +2458,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2497,22 +2497,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3208,17 +3208,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3327,17 +3327,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4624,17 +4624,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>141.7</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4976,17 +4976,17 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5215,17 +5215,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5448,22 +5448,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5691,17 +5691,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5805,7 +5805,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -5885,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6048,17 +6048,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -6123,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -6361,7 +6361,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -6653,7 +6653,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -6772,7 +6772,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -6837,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7246,17 +7246,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7321,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7375,7 +7375,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7440,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7484,17 +7484,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7613,7 +7613,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -7678,7 +7678,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7722,17 +7722,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -7797,7 +7797,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -8035,7 +8035,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8079,17 +8079,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -8273,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8317,17 +8317,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>141.7</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -8511,7 +8511,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8684,7 +8684,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -8872,7 +8872,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8987,7 +8987,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9146,17 +9146,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -9221,7 +9221,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9340,7 +9340,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9459,7 +9459,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -9578,7 +9578,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9697,7 +9697,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -9935,7 +9935,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10027,24 +10027,24 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10093,17 +10093,17 @@
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA81" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -10169,7 +10169,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -10251,32 +10251,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -10284,7 +10288,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10308,37 +10312,37 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -10366,32 +10370,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:43</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -10399,7 +10407,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10423,17 +10431,17 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
@@ -10443,17 +10451,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -10481,32 +10489,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -10514,7 +10526,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10538,17 +10550,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10558,17 +10570,17 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -10596,32 +10608,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10629,7 +10645,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10653,17 +10669,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10673,17 +10689,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -10711,32 +10727,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -10744,7 +10764,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10768,17 +10788,17 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -10788,17 +10808,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -10826,32 +10846,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10859,7 +10883,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10883,17 +10907,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10903,17 +10927,17 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>141.7</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -11028,7 +11052,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -11089,7 +11113,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11128,7 +11152,7 @@
       </c>
       <c r="Z90" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA90" s="2" t="inlineStr">
@@ -11143,7 +11167,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -11171,32 +11195,36 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:36</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11204,7 +11232,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11228,17 +11256,17 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11248,17 +11276,17 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -11319,7 +11347,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11373,7 +11401,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -11434,7 +11462,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11549,7 +11577,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11664,7 +11692,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11779,7 +11807,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11894,7 +11922,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -12009,7 +12037,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12063,7 +12091,7 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -12124,7 +12152,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12239,7 +12267,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12297,6 +12325,466 @@
         </is>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>134.5</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>5/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>12/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>140.5</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>15/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>10/30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-26-浦东35路.xlsx
+++ b/data/export/2026-10-26-浦东35路.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -2458,7 +2458,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3799,17 +3799,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5572,17 +5572,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -5885,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -6123,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -6361,7 +6361,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -7321,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7375,7 +7375,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7603,17 +7603,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7732,7 +7732,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -7797,7 +7797,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -8327,7 +8327,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -8511,7 +8511,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8872,7 +8872,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8987,7 +8987,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -9221,7 +9221,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9340,7 +9340,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9384,17 +9384,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -9459,7 +9459,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -9578,7 +9578,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9697,7 +9697,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9935,7 +9935,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10108,7 +10108,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -10288,7 +10288,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10461,7 +10461,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -10818,7 +10818,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -10937,7 +10937,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -11113,7 +11113,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11167,7 +11167,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -11205,24 +11205,24 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>20:36</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -11232,7 +11232,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -11314,32 +11314,36 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:48</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -11347,7 +11351,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11371,17 +11375,17 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
@@ -11391,17 +11395,17 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -11429,32 +11433,36 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:57</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11462,7 +11470,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11486,17 +11494,17 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -11506,17 +11514,17 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11585,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11659,12 +11667,12 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq28推进至seq37，推进9站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -11692,7 +11700,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11700,10 +11708,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q95" s="2" t="inlineStr"/>
-      <c r="R95" s="2" t="inlineStr"/>
-      <c r="S95" s="2" t="inlineStr"/>
-      <c r="T95" s="2" t="inlineStr"/>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>物理seq31（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr">
+        <is>
+          <t>20:13</t>
+        </is>
+      </c>
+      <c r="S95" s="2" t="inlineStr">
+        <is>
+          <t>20:17</t>
+        </is>
+      </c>
+      <c r="T95" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq31映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U95" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -11807,7 +11831,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11922,7 +11946,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -12037,7 +12061,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12091,7 +12115,7 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -12152,7 +12176,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12267,7 +12291,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12382,7 +12406,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12497,7 +12521,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12551,7 +12575,7 @@
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -12612,7 +12636,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12727,7 +12751,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12781,7 +12805,7 @@
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-26-浦东35路.xlsx
+++ b/data/export/2026-10-26-浦东35路.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1657,17 +1657,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1895,17 +1895,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>144.2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -2458,7 +2458,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4862,17 +4862,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5100,17 +5100,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>144.2</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5334,17 +5334,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -6534,7 +6534,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -7797,7 +7797,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -8327,7 +8327,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -8511,7 +8511,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8555,17 +8555,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>144.2</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -8872,7 +8872,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8916,17 +8916,17 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -8987,7 +8987,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9156,7 +9156,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -9221,7 +9221,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9578,7 +9578,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9632,7 +9632,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -9697,7 +9697,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9741,17 +9741,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -9935,7 +9935,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9989,7 +9989,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -10054,7 +10054,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10288,7 +10288,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10342,7 +10342,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -10699,7 +10699,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -10937,7 +10937,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -11113,7 +11113,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11286,7 +11286,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -11552,32 +11552,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -11585,7 +11589,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11609,17 +11613,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11629,17 +11633,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>144.2</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -11672,7 +11676,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq28推进至seq37，推进9站，达到≥2站确认条件</t>
+          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq28推进至seq61，推进33站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -11700,7 +11704,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11770,7 +11774,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -11798,32 +11802,36 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:23</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -11831,7 +11839,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11855,17 +11863,17 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -11875,17 +11883,17 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -11913,32 +11921,36 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:27</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -11946,7 +11958,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11970,17 +11982,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -11990,17 +12002,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -12176,7 +12188,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12291,7 +12303,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12345,7 +12357,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -12406,7 +12418,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12521,7 +12533,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12636,7 +12648,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12690,7 +12702,7 @@
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -12751,7 +12763,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
